--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/05 Mayo/Liquidacióncvs - VENTAS/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/05 Mayo/Liquidacióncvs - FINAL/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="952" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33AF4B0C-4B7D-42E9-A844-F40857C354B4}"/>
+  <xr:revisionPtr revIDLastSave="961" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7900915A-B619-44E7-9742-15B5EBF126DD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -570,7 +570,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="2">
-        <v>1500</v>
+        <v>875</v>
       </c>
       <c r="E2" s="2">
         <v>3000</v>
@@ -2015,7 +2015,7 @@
         <v>22</v>
       </c>
       <c r="D87" s="2">
-        <v>1500</v>
+        <v>1125</v>
       </c>
       <c r="E87" s="2">
         <v>3500</v>
@@ -2185,7 +2185,7 @@
         <v>22</v>
       </c>
       <c r="D97" s="2">
-        <v>1500</v>
+        <v>312</v>
       </c>
       <c r="E97" s="2">
         <v>6800</v>
